--- a/docs/bond_design/付着設計問題集.xlsx
+++ b/docs/bond_design/付着設計問題集.xlsx
@@ -241,6 +241,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -271,6 +274,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -284,10 +290,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7429500" cy="3571875"/>
+    <ext cx="8191500" cy="3486150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -317,6 +323,39 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="7429500" cy="3571875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="7810500" cy="3028950"/>
     <pic>
       <nvPicPr>
@@ -331,6 +370,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1193,8 +1235,8 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A53:H53"/>
@@ -1217,7 +1259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1381,9 +1423,17 @@
         </is>
       </c>
     </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>■ 補足図（理解の整理）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A10:H10"/>
@@ -1397,6 +1447,7 @@
     <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1879,15 +1930,15 @@
     <mergeCell ref="A56:H56"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="A38:H38"/>
     <mergeCell ref="A54:H54"/>
     <mergeCell ref="A47:H47"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
